--- a/education_forms/011_child_education_case_research_consent_form--education_forms.xlsx
+++ b/education_forms/011_child_education_case_research_consent_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -889,8 +889,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -918,12 +918,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_i_consent',_'value':_true}</t>
+          <t>yes_-_i_consent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - I Consent', 'value': True}</t>
+          <t>Yes - I Consent</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_i_do_not_consent',_'value':_false}</t>
+          <t>no_-_i_do_not_consent</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'No - I Do Not Consent', 'value': False}</t>
+          <t>No - I Do Not Consent</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'one-on-one_interviews',_'value':_'interviews'}</t>
+          <t>one-on-one_interviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'One-on-one Interviews', 'value': 'interviews'}</t>
+          <t>One-on-one Interviews</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'classroom_observation',_'value':_'observation'}</t>
+          <t>classroom_observation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Classroom Observation', 'value': 'observation'}</t>
+          <t>Classroom Observation</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'collection_of_academic_data',_'value':_'data'}</t>
+          <t>collection_of_academic_data</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Collection of Academic Data', 'value': 'data'}</t>
+          <t>Collection of Academic Data</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'standardized_testing',_'value':_'testing'}</t>
+          <t>standardized_testing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Standardized Testing', 'value': 'testing'}</t>
+          <t>Standardized Testing</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_audio_and_video',_'value':_'both'}</t>
+          <t>yes_-_audio_and_video</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Audio and Video', 'value': 'both'}</t>
+          <t>Yes - Audio and Video</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_audio_only',_'value':_'audio'}</t>
+          <t>yes_-_audio_only</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Audio Only', 'value': 'audio'}</t>
+          <t>Yes - Audio Only</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'no_recording_allowed',_'value':_'none'}</t>
+          <t>no_recording_allowed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'No Recording Allowed', 'value': 'none'}</t>
+          <t>No Recording Allowed</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
